--- a/data/trans_dic/PCS12_SP_R3-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/PCS12_SP_R3-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población en el primer cuartil (49.019) de la puntuación del componente de salud física (SF12)</t>
+          <t>Población en el primer cuartil (49.019) de la puntuación del componente de salud física (SF12) (tasa de respuesta: 99,81%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>29,12; 34,74</t>
+          <t>29,32; 35,05</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>32,59; 39,44</t>
+          <t>32,69; 39,45</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>32,48; 39,35</t>
+          <t>32,86; 39,99</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>41,23; 49,41</t>
+          <t>40,75; 49,26</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>46,33; 51,57</t>
+          <t>45,92; 51,5</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>49,45; 55,06</t>
+          <t>49,63; 55,18</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>47,7; 54,31</t>
+          <t>47,66; 54,43</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>58,45; 64,01</t>
+          <t>58,12; 63,67</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>39,6; 43,56</t>
+          <t>39,52; 43,56</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>43,38; 47,56</t>
+          <t>43,47; 47,79</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>42,12; 46,92</t>
+          <t>42,02; 46,94</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>52,29; 56,97</t>
+          <t>52,24; 57,41</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,34; 10,07</t>
+          <t>7,22; 10,02</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>9,58; 12,5</t>
+          <t>9,55; 12,45</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10,51; 13,2</t>
+          <t>10,44; 13,35</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17,82; 49,72</t>
+          <t>17,87; 51,37</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>12,0; 15,49</t>
+          <t>11,96; 15,27</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,75; 18,45</t>
+          <t>14,5; 18,25</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,63; 19,28</t>
+          <t>15,81; 19,26</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>15,19; 23,72</t>
+          <t>15,08; 23,71</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>9,88; 12,14</t>
+          <t>9,97; 12,16</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12,32; 14,76</t>
+          <t>12,39; 14,73</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13,43; 15,75</t>
+          <t>13,55; 15,84</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>18,93; 40,04</t>
+          <t>18,9; 36,17</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,46; 10,29</t>
+          <t>5,46; 10,31</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,84; 12,51</t>
+          <t>6,92; 13,03</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,25; 11,23</t>
+          <t>6,32; 11,72</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10,23; 15,32</t>
+          <t>10,35; 15,65</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9,38; 15,77</t>
+          <t>9,81; 15,65</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,1; 12,58</t>
+          <t>7,08; 12,56</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,91; 15,96</t>
+          <t>9,8; 16,01</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>13,61; 18,32</t>
+          <t>13,52; 18,05</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7,9; 11,96</t>
+          <t>8,04; 12,1</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7,64; 11,81</t>
+          <t>7,65; 11,82</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8,69; 13,04</t>
+          <t>8,45; 12,52</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>12,54; 15,91</t>
+          <t>12,6; 16,1</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>14,65; 17,11</t>
+          <t>14,48; 17,12</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>16,53; 19,26</t>
+          <t>16,61; 19,25</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15,24; 17,97</t>
+          <t>15,5; 18,02</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>21,13; 45,12</t>
+          <t>21,18; 44,14</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>25,62; 28,75</t>
+          <t>25,71; 28,81</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>27,45; 30,51</t>
+          <t>27,58; 30,68</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>24,67; 27,65</t>
+          <t>24,51; 27,7</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>22,97; 30,38</t>
+          <t>23,24; 30,42</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>20,52; 22,62</t>
+          <t>20,48; 22,61</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>22,59; 24,6</t>
+          <t>22,6; 24,6</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>20,52; 22,61</t>
+          <t>20,58; 22,52</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>24,56; 36,15</t>
+          <t>24,48; 35,65</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población en el primer cuartil (49.019) de la puntuación del componente de salud física (SF12)</t>
+          <t>Población en el primer cuartil (49.019) de la puntuación del componente de salud física (SF12) (tasa de respuesta: 99,81%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>300418; 358421</t>
+          <t>302478; 361658</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>317654; 384404</t>
+          <t>318618; 384488</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>245010; 296839</t>
+          <t>247873; 301683</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>210442; 252184</t>
+          <t>207994; 251427</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>609290; 678170</t>
+          <t>603850; 677323</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>661603; 736544</t>
+          <t>663931; 738197</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>474406; 540171</t>
+          <t>474024; 541352</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>435797; 477215</t>
+          <t>433321; 474699</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>929251; 1022323</t>
+          <t>927379; 1022209</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1003107; 1099750</t>
+          <t>1005314; 1105154</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>736660; 820669</t>
+          <t>734966; 820981</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>656676; 715523</t>
+          <t>656169; 721062</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>124248; 170490</t>
+          <t>122267; 169657</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>188056; 245589</t>
+          <t>187482; 244504</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>218245; 274005</t>
+          <t>216865; 277288</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>406473; 1134287</t>
+          <t>407640; 1172065</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>190521; 245874</t>
+          <t>189844; 242407</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>259237; 324256</t>
+          <t>254967; 320748</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>310869; 383368</t>
+          <t>314408; 382995</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>339150; 529555</t>
+          <t>336547; 529266</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>324217; 398363</t>
+          <t>327281; 399022</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>458663; 549159</t>
+          <t>461118; 548152</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>545687; 640185</t>
+          <t>550823; 643813</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>854580; 1807451</t>
+          <t>852994; 1632443</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>30094; 56762</t>
+          <t>30108; 56852</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>32889; 60219</t>
+          <t>33282; 62688</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>34169; 61397</t>
+          <t>34539; 64111</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>65900; 98714</t>
+          <t>66726; 100838</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>44704; 75139</t>
+          <t>46754; 74577</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>32555; 57685</t>
+          <t>32467; 57604</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>54426; 87616</t>
+          <t>53832; 87897</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>89493; 120467</t>
+          <t>88902; 118685</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>81217; 122954</t>
+          <t>82659; 124404</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>71771; 111021</t>
+          <t>71908; 111056</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>95197; 142915</t>
+          <t>92624; 137182</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>163256; 207158</t>
+          <t>164064; 209578</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>479996; 560644</t>
+          <t>474454; 560810</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>565188; 658719</t>
+          <t>568040; 658322</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>514660; 607001</t>
+          <t>523684; 608559</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>726030; 1550498</t>
+          <t>727858; 1516925</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>865860; 971428</t>
+          <t>868738; 973390</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>975482; 1084477</t>
+          <t>980236; 1090559</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>871445; 976704</t>
+          <t>865827; 978388</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>835105; 1104369</t>
+          <t>844777; 1105800</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1365870; 1505658</t>
+          <t>1362956; 1504916</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1575258; 1715690</t>
+          <t>1575971; 1715349</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1418076; 1562407</t>
+          <t>1422166; 1556244</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1736497; 2556680</t>
+          <t>1730995; 2520879</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/PCS12_SP_R3-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/PCS12_SP_R3-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>45,01%</t>
+          <t>42,71%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>61,03%</t>
+          <t>60,15%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>54,52%</t>
+          <t>52,93%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>29,32; 35,05</t>
+          <t>29,37; 35,01</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>32,69; 39,45</t>
+          <t>33,22; 39,53</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>32,86; 39,99</t>
+          <t>33,01; 39,53</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>40,75; 49,26</t>
+          <t>38,43; 46,56</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>45,92; 51,5</t>
+          <t>46,3; 51,79</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>49,63; 55,18</t>
+          <t>49,63; 55,22</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>47,66; 54,43</t>
+          <t>47,81; 54,49</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>58,12; 63,67</t>
+          <t>57,33; 63,03</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>39,52; 43,56</t>
+          <t>39,71; 43,57</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>43,47; 47,79</t>
+          <t>43,38; 47,59</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>42,02; 46,94</t>
+          <t>42,11; 46,94</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>52,24; 57,41</t>
+          <t>50,61; 55,18</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>23,6%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>20,93%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,22; 10,02</t>
+          <t>7,43; 10,14</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>9,55; 12,45</t>
+          <t>9,41; 12,4</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10,44; 13,35</t>
+          <t>10,57; 13,42</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17,87; 51,37</t>
+          <t>16,71; 20,05</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>11,96; 15,27</t>
+          <t>11,88; 15,35</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,5; 18,25</t>
+          <t>14,82; 18,44</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,81; 19,26</t>
+          <t>15,63; 19,2</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>15,08; 23,71</t>
+          <t>22,05; 25,25</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>9,97; 12,16</t>
+          <t>9,98; 12,1</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12,39; 14,73</t>
+          <t>12,39; 14,76</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13,55; 15,84</t>
+          <t>13,44; 15,77</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>18,9; 36,17</t>
+          <t>19,83; 22,17</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,88%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,46; 10,31</t>
+          <t>5,5; 10,26</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,92; 13,03</t>
+          <t>7,02; 12,95</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,32; 11,72</t>
+          <t>5,8; 11,09</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10,35; 15,65</t>
+          <t>10,38; 15,51</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9,81; 15,65</t>
+          <t>9,72; 15,85</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,08; 12,56</t>
+          <t>7,0; 12,67</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,8; 16,01</t>
+          <t>9,82; 15,58</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>13,52; 18,05</t>
+          <t>14,67; 19,59</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8,04; 12,1</t>
+          <t>8,07; 11,86</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7,65; 11,82</t>
+          <t>7,59; 11,77</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8,45; 12,52</t>
+          <t>8,56; 12,64</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>12,6; 16,1</t>
+          <t>13,22; 16,66</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>27,12%</t>
+          <t>21,21%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>28,04%</t>
+          <t>30,27%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>25,87%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>14,48; 17,12</t>
+          <t>14,68; 17,18</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>16,61; 19,25</t>
+          <t>16,55; 19,31</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15,5; 18,02</t>
+          <t>15,47; 18,13</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>21,18; 44,14</t>
+          <t>19,87; 22,61</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>25,71; 28,81</t>
+          <t>25,72; 28,95</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>27,58; 30,68</t>
+          <t>27,66; 30,64</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>24,51; 27,7</t>
+          <t>24,58; 27,8</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>23,24; 30,42</t>
+          <t>28,97; 31,5</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>20,48; 22,61</t>
+          <t>20,61; 22,62</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>22,6; 24,6</t>
+          <t>22,56; 24,61</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>20,58; 22,52</t>
+          <t>20,51; 22,6</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>24,48; 35,65</t>
+          <t>24,87; 26,83</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>229727</t>
+          <t>244969</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>455030</t>
+          <t>488081</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>684756</t>
+          <t>733050</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>302478; 361658</t>
+          <t>303011; 361221</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>318618; 384488</t>
+          <t>323758; 385275</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>247873; 301683</t>
+          <t>248988; 298181</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>207994; 251427</t>
+          <t>220428; 267069</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>603850; 677323</t>
+          <t>608852; 681078</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>663931; 738197</t>
+          <t>663909; 738763</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>474024; 541352</t>
+          <t>475542; 541964</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>433321; 474699</t>
+          <t>465187; 511464</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>927379; 1022209</t>
+          <t>931865; 1022480</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1005314; 1105154</t>
+          <t>1003239; 1100508</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>734966; 820981</t>
+          <t>736577; 821002</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>656169; 721062</t>
+          <t>700950; 764253</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>620057</t>
+          <t>407049</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>460709</t>
+          <t>511141</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1080766</t>
+          <t>918190</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>122267; 169657</t>
+          <t>125837; 171736</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>187482; 244504</t>
+          <t>184885; 243573</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>216865; 277288</t>
+          <t>219563; 278695</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>407640; 1172065</t>
+          <t>371074; 445340</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>189844; 242407</t>
+          <t>188680; 243637</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>254967; 320748</t>
+          <t>260505; 324214</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>314408; 382995</t>
+          <t>310698; 381826</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>336547; 529266</t>
+          <t>477577; 546849</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>327281; 399022</t>
+          <t>327538; 397094</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>461118; 548152</t>
+          <t>461239; 549406</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>550823; 643813</t>
+          <t>546307; 641165</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>852994; 1632443</t>
+          <t>869850; 972622</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>82305</t>
+          <t>91171</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>103442</t>
+          <t>123287</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>185747</t>
+          <t>214458</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>30108; 56852</t>
+          <t>30343; 56558</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>33282; 62688</t>
+          <t>33778; 62317</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>34539; 64111</t>
+          <t>31693; 60660</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>66726; 100838</t>
+          <t>73582; 109989</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>46754; 74577</t>
+          <t>46298; 75491</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>32467; 57604</t>
+          <t>32097; 58098</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>53832; 87897</t>
+          <t>53900; 85574</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>88902; 118685</t>
+          <t>107363; 143383</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>82659; 124404</t>
+          <t>82964; 121905</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>71908; 111056</t>
+          <t>71318; 110576</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>92624; 137182</t>
+          <t>93773; 138531</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>164064; 209578</t>
+          <t>190507; 240126</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>932089</t>
+          <t>743189</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>1019181</t>
+          <t>1122508</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1951270</t>
+          <t>1865697</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>474454; 560810</t>
+          <t>481030; 562924</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>568040; 658322</t>
+          <t>565940; 660424</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>523684; 608559</t>
+          <t>522465; 612327</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>727858; 1516925</t>
+          <t>696095; 792352</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>868738; 973390</t>
+          <t>869194; 978300</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>980236; 1090559</t>
+          <t>983118; 1088958</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>865827; 978388</t>
+          <t>868353; 982059</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>844777; 1105800</t>
+          <t>1074414; 1168226</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1362956; 1504916</t>
+          <t>1371871; 1505426</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1575971; 1715349</t>
+          <t>1573601; 1716594</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1422166; 1556244</t>
+          <t>1417239; 1561272</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1730995; 2520879</t>
+          <t>1793589; 1934735</t>
         </is>
       </c>
     </row>
